--- a/premium/telechargement/budget-mensuel.xlsx
+++ b/premium/telechargement/budget-mensuel.xlsx
@@ -9,6 +9,8 @@
   <sheets>
     <sheet name="Budget 2026" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Guide" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Tableau de bord" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Abonnements" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Budget 2026'!$A$1:$E$97</definedName>
@@ -20,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +43,19 @@
       <b val="1"/>
       <sz val="14"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -57,6 +70,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFD60A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -86,12 +104,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -180,6 +205,91 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Réel dépensé par catégorie</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2711,4 +2821,380 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Dépenses annuelles par catégorie (Réel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Catégorie</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Prévu (€)</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Réel (€)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Loyer</t>
+        </is>
+      </c>
+      <c r="B4" s="2">
+        <f>SUMIF('Budget 2026'!B2:B97,A4,'Budget 2026'!C2:C97)</f>
+        <v/>
+      </c>
+      <c r="C4" s="2">
+        <f>SUMIF('Budget 2026'!B2:B97,A4,'Budget 2026'!D2:D97)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Courses</t>
+        </is>
+      </c>
+      <c r="B5" s="2">
+        <f>SUMIF('Budget 2026'!B2:B97,A5,'Budget 2026'!C2:C97)</f>
+        <v/>
+      </c>
+      <c r="C5" s="2">
+        <f>SUMIF('Budget 2026'!B2:B97,A5,'Budget 2026'!D2:D97)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="B6" s="2">
+        <f>SUMIF('Budget 2026'!B2:B97,A6,'Budget 2026'!C2:C97)</f>
+        <v/>
+      </c>
+      <c r="C6" s="2">
+        <f>SUMIF('Budget 2026'!B2:B97,A6,'Budget 2026'!D2:D97)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Abonnements</t>
+        </is>
+      </c>
+      <c r="B7" s="2">
+        <f>SUMIF('Budget 2026'!B2:B97,A7,'Budget 2026'!C2:C97)</f>
+        <v/>
+      </c>
+      <c r="C7" s="2">
+        <f>SUMIF('Budget 2026'!B2:B97,A7,'Budget 2026'!D2:D97)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Santé</t>
+        </is>
+      </c>
+      <c r="B8" s="2">
+        <f>SUMIF('Budget 2026'!B2:B97,A8,'Budget 2026'!C2:C97)</f>
+        <v/>
+      </c>
+      <c r="C8" s="2">
+        <f>SUMIF('Budget 2026'!B2:B97,A8,'Budget 2026'!D2:D97)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Loisirs</t>
+        </is>
+      </c>
+      <c r="B9" s="2">
+        <f>SUMIF('Budget 2026'!B2:B97,A9,'Budget 2026'!C2:C97)</f>
+        <v/>
+      </c>
+      <c r="C9" s="2">
+        <f>SUMIF('Budget 2026'!B2:B97,A9,'Budget 2026'!D2:D97)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Shopping</t>
+        </is>
+      </c>
+      <c r="B10" s="2">
+        <f>SUMIF('Budget 2026'!B2:B97,A10,'Budget 2026'!C2:C97)</f>
+        <v/>
+      </c>
+      <c r="C10" s="2">
+        <f>SUMIF('Budget 2026'!B2:B97,A10,'Budget 2026'!D2:D97)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Épargne</t>
+        </is>
+      </c>
+      <c r="B11" s="2">
+        <f>SUMIF('Budget 2026'!B2:B97,A11,'Budget 2026'!C2:C97)</f>
+        <v/>
+      </c>
+      <c r="C11" s="2">
+        <f>SUMIF('Budget 2026'!B2:B97,A11,'Budget 2026'!D2:D97)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B12" s="6">
+        <f>SUM(B4:B11)</f>
+        <v/>
+      </c>
+      <c r="C12" s="6">
+        <f>SUM(C4:C11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Taux d'épargne réel</t>
+        </is>
+      </c>
+      <c r="C14" s="8">
+        <f>SUMIF('Budget 2026'!B2:B97,"Épargne",'Budget 2026'!D2:D97)/C12</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Tous tes abonnements : garde ou résilie (l'économie se calcule seule)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>€ / mois</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>€ / an</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>Je garde ? (Oui/Non)</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>Économisé si résilié</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Netflix</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>13.49</v>
+      </c>
+      <c r="C4" s="2">
+        <f>B4*12</f>
+        <v/>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="E4" s="10">
+        <f>IF(D4="Non",C4,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Spotify</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>11.12</v>
+      </c>
+      <c r="C5" s="2">
+        <f>B5*12</f>
+        <v/>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="E5" s="10">
+        <f>IF(D5="Non",C5,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Salle de sport</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="C6" s="2">
+        <f>B6*12</f>
+        <v/>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="E6" s="10">
+        <f>IF(D6="Non",C6,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Stockage cloud</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="C7" s="2">
+        <f>B7*12</f>
+        <v/>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="E7" s="10">
+        <f>IF(D7="Non",C7,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>À compléter</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="2">
+        <f>B8*12</f>
+        <v/>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="E8" s="10">
+        <f>IF(D8="Non",C8,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>ÉCONOMIE ANNUELLE SI RÉSILIATION</t>
+        </is>
+      </c>
+      <c r="E10" s="11">
+        <f>SUM(E4:E9)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="D4:D9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Oui,Non"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>